--- a/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-19T09:04:56+00:00</t>
+    <t>2024-02-19T13:34:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-19T13:34:28+00:00</t>
+    <t>2024-02-19T13:42:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-19T13:42:29+00:00</t>
+    <t>2024-03-04T16:55:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-04T16:55:03+00:00</t>
+    <t>2024-03-05T15:34:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-05T15:34:40+00:00</t>
+    <t>2024-03-06T10:45:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-06T10:45:14+00:00</t>
+    <t>2024-03-07T10:27:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-07T10:27:01+00:00</t>
+    <t>2024-03-12T12:54:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T12:54:34+00:00</t>
+    <t>2024-03-12T13:20:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T13:20:54+00:00</t>
+    <t>2024-03-12T13:39:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T13:39:01+00:00</t>
+    <t>2024-03-12T13:58:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T13:58:30+00:00</t>
+    <t>2024-03-12T14:02:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T14:02:45+00:00</t>
+    <t>2024-03-12T14:08:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T14:08:02+00:00</t>
+    <t>2024-03-12T14:13:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T14:13:18+00:00</t>
+    <t>2024-03-12T14:29:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T14:29:58+00:00</t>
+    <t>2024-03-12T16:57:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T16:57:02+00:00</t>
+    <t>2024-03-12T17:28:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T17:28:16+00:00</t>
+    <t>2024-03-13T08:21:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -57,13 +57,13 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-13T08:21:45+00:00</t>
+    <t>2024-03-13T15:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>ANS</t>
+    <t>Agence du Numérique en Santé (ANS) - 2-10 Rue d'Oradour-sur-Glane, 75015 Paris</t>
   </si>
   <si>
     <t>Contact</t>

--- a/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-13T15:21:15+00:00</t>
+    <t>2024-03-13T15:40:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-13T15:40:01+00:00</t>
+    <t>2024-03-15T14:37:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-02T13:53:07+00:00</t>
+    <t>2024-04-02T14:01:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0-ballot-4</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-02T14:01:28+00:00</t>
+    <t>2024-04-03T13:55:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-08T12:41:20+00:00</t>
+    <t>2024-04-08T12:53:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-08T12:53:48+00:00</t>
+    <t>2024-04-09T07:46:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -319,9 +319,6 @@
     <t>Element.extension</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t>Extension.extension:endDate</t>
   </si>
   <si>
@@ -363,6 +360,9 @@
   </si>
   <si>
     <t>Extension.url</t>
+  </si>
+  <si>
+    <t>N/A</t>
   </si>
   <si>
     <t>Extension.extension:endDate.value[x]</t>
@@ -1177,24 +1177,24 @@
         <v>78</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ4" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AK4" t="s" s="2">
-        <v>99</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B5" t="s" s="2">
         <v>89</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D5" t="s" s="2">
         <v>76</v>
@@ -1222,7 +1222,7 @@
         <v>30</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1282,7 +1282,7 @@
         <v>78</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ5" t="s" s="2">
         <v>81</v>
@@ -1293,10 +1293,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="B6" t="s" s="2">
         <v>103</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>104</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1396,10 +1396,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="B7" t="s" s="2">
         <v>105</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>106</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1428,7 +1428,7 @@
         <v>30</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1488,7 +1488,7 @@
         <v>78</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ7" t="s" s="2">
         <v>81</v>
@@ -1499,10 +1499,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="B8" t="s" s="2">
         <v>107</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>108</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1525,16 +1525,16 @@
         <v>76</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L8" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="M8" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="M8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>111</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>112</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="S8" t="s" s="2">
         <v>76</v>
@@ -1584,7 +1584,7 @@
         <v>76</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>83</v>
@@ -1599,7 +1599,7 @@
         <v>76</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>99</v>
+        <v>113</v>
       </c>
     </row>
     <row r="9">
@@ -1696,13 +1696,13 @@
         <v>83</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ9" t="s" s="2">
         <v>120</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>99</v>
+        <v>113</v>
       </c>
     </row>
     <row r="10">
@@ -1741,7 +1741,7 @@
         <v>30</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1801,7 +1801,7 @@
         <v>78</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>81</v>
@@ -1815,7 +1815,7 @@
         <v>123</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1918,7 +1918,7 @@
         <v>124</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1947,7 +1947,7 @@
         <v>30</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2007,7 +2007,7 @@
         <v>78</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>81</v>
@@ -2021,7 +2021,7 @@
         <v>125</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2044,16 +2044,16 @@
         <v>76</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L13" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="M13" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>111</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>112</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2103,7 +2103,7 @@
         <v>76</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>83</v>
@@ -2118,7 +2118,7 @@
         <v>76</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>99</v>
+        <v>113</v>
       </c>
     </row>
     <row r="14">
@@ -2215,21 +2215,21 @@
         <v>83</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>120</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>99</v>
+        <v>113</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2252,16 +2252,16 @@
         <v>76</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L15" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="M15" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>111</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>112</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -2311,7 +2311,7 @@
         <v>76</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>83</v>
@@ -2326,7 +2326,7 @@
         <v>76</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>99</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -2423,13 +2423,13 @@
         <v>83</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ16" t="s" s="2">
         <v>120</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>99</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>

--- a/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-09T07:46:55+00:00</t>
+    <t>2024-04-10T12:18:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -319,6 +319,9 @@
     <t>Element.extension</t>
   </si>
   <si>
+    <t>N/A</t>
+  </si>
+  <si>
     <t>Extension.extension:endDate</t>
   </si>
   <si>
@@ -360,9 +363,6 @@
   </si>
   <si>
     <t>Extension.url</t>
-  </si>
-  <si>
-    <t>N/A</t>
   </si>
   <si>
     <t>Extension.extension:endDate.value[x]</t>
@@ -1177,24 +1177,24 @@
         <v>78</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ4" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AK4" t="s" s="2">
-        <v>88</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B5" t="s" s="2">
         <v>89</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D5" t="s" s="2">
         <v>76</v>
@@ -1222,7 +1222,7 @@
         <v>30</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1282,7 +1282,7 @@
         <v>78</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ5" t="s" s="2">
         <v>81</v>
@@ -1293,10 +1293,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1396,10 +1396,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1428,7 +1428,7 @@
         <v>30</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1488,7 +1488,7 @@
         <v>78</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ7" t="s" s="2">
         <v>81</v>
@@ -1499,10 +1499,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1525,16 +1525,16 @@
         <v>76</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="S8" t="s" s="2">
         <v>76</v>
@@ -1584,7 +1584,7 @@
         <v>76</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>83</v>
@@ -1599,7 +1599,7 @@
         <v>76</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>113</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9">
@@ -1696,13 +1696,13 @@
         <v>83</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ9" t="s" s="2">
         <v>120</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>113</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10">
@@ -1741,7 +1741,7 @@
         <v>30</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1801,7 +1801,7 @@
         <v>78</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>81</v>
@@ -1815,7 +1815,7 @@
         <v>123</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1918,7 +1918,7 @@
         <v>124</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1947,7 +1947,7 @@
         <v>30</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2007,7 +2007,7 @@
         <v>78</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>81</v>
@@ -2021,7 +2021,7 @@
         <v>125</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2044,16 +2044,16 @@
         <v>76</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2103,7 +2103,7 @@
         <v>76</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>83</v>
@@ -2118,7 +2118,7 @@
         <v>76</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>113</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -2215,21 +2215,21 @@
         <v>83</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>120</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>113</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2252,16 +2252,16 @@
         <v>76</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -2311,7 +2311,7 @@
         <v>76</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>83</v>
@@ -2326,7 +2326,7 @@
         <v>76</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>113</v>
+        <v>99</v>
       </c>
     </row>
     <row r="16">
@@ -2423,13 +2423,13 @@
         <v>83</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ16" t="s" s="2">
         <v>120</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>113</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>

--- a/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T12:18:24+00:00</t>
+    <t>2024-04-10T12:37:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -319,9 +319,6 @@
     <t>Element.extension</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t>Extension.extension:endDate</t>
   </si>
   <si>
@@ -363,6 +360,9 @@
   </si>
   <si>
     <t>Extension.url</t>
+  </si>
+  <si>
+    <t>N/A</t>
   </si>
   <si>
     <t>Extension.extension:endDate.value[x]</t>
@@ -1177,24 +1177,24 @@
         <v>78</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ4" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AK4" t="s" s="2">
-        <v>99</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B5" t="s" s="2">
         <v>89</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D5" t="s" s="2">
         <v>76</v>
@@ -1222,7 +1222,7 @@
         <v>30</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1282,7 +1282,7 @@
         <v>78</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ5" t="s" s="2">
         <v>81</v>
@@ -1293,10 +1293,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="B6" t="s" s="2">
         <v>103</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>104</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1396,10 +1396,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="B7" t="s" s="2">
         <v>105</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>106</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1428,7 +1428,7 @@
         <v>30</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1488,7 +1488,7 @@
         <v>78</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ7" t="s" s="2">
         <v>81</v>
@@ -1499,10 +1499,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="B8" t="s" s="2">
         <v>107</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>108</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1525,16 +1525,16 @@
         <v>76</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L8" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="M8" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="M8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>111</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>112</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="S8" t="s" s="2">
         <v>76</v>
@@ -1584,7 +1584,7 @@
         <v>76</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>83</v>
@@ -1599,7 +1599,7 @@
         <v>76</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>99</v>
+        <v>113</v>
       </c>
     </row>
     <row r="9">
@@ -1696,13 +1696,13 @@
         <v>83</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ9" t="s" s="2">
         <v>120</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>99</v>
+        <v>113</v>
       </c>
     </row>
     <row r="10">
@@ -1741,7 +1741,7 @@
         <v>30</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1801,7 +1801,7 @@
         <v>78</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>81</v>
@@ -1815,7 +1815,7 @@
         <v>123</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1918,7 +1918,7 @@
         <v>124</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1947,7 +1947,7 @@
         <v>30</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2007,7 +2007,7 @@
         <v>78</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>81</v>
@@ -2021,7 +2021,7 @@
         <v>125</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2044,16 +2044,16 @@
         <v>76</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L13" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="M13" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>111</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>112</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2103,7 +2103,7 @@
         <v>76</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>83</v>
@@ -2118,7 +2118,7 @@
         <v>76</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>99</v>
+        <v>113</v>
       </c>
     </row>
     <row r="14">
@@ -2215,21 +2215,21 @@
         <v>83</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>120</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>99</v>
+        <v>113</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2252,16 +2252,16 @@
         <v>76</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L15" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="M15" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>111</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>112</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -2311,7 +2311,7 @@
         <v>76</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>83</v>
@@ -2326,7 +2326,7 @@
         <v>76</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>99</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -2423,13 +2423,13 @@
         <v>83</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ16" t="s" s="2">
         <v>120</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>99</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>

--- a/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T18:21:45+00:00</t>
+    <t>2024-04-18T13:43:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-18T13:43:00+00:00</t>
+    <t>2024-04-25T11:33:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -319,6 +319,9 @@
     <t>Element.extension</t>
   </si>
   <si>
+    <t>N/A</t>
+  </si>
+  <si>
     <t>Extension.extension:endDate</t>
   </si>
   <si>
@@ -360,9 +363,6 @@
   </si>
   <si>
     <t>Extension.url</t>
-  </si>
-  <si>
-    <t>N/A</t>
   </si>
   <si>
     <t>Extension.extension:endDate.value[x]</t>
@@ -1177,24 +1177,24 @@
         <v>78</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ4" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AK4" t="s" s="2">
-        <v>88</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B5" t="s" s="2">
         <v>89</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D5" t="s" s="2">
         <v>76</v>
@@ -1222,7 +1222,7 @@
         <v>30</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1282,7 +1282,7 @@
         <v>78</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ5" t="s" s="2">
         <v>81</v>
@@ -1293,10 +1293,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1396,10 +1396,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1428,7 +1428,7 @@
         <v>30</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1488,7 +1488,7 @@
         <v>78</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ7" t="s" s="2">
         <v>81</v>
@@ -1499,10 +1499,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1525,16 +1525,16 @@
         <v>76</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="S8" t="s" s="2">
         <v>76</v>
@@ -1584,7 +1584,7 @@
         <v>76</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>83</v>
@@ -1599,7 +1599,7 @@
         <v>76</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>113</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9">
@@ -1696,13 +1696,13 @@
         <v>83</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ9" t="s" s="2">
         <v>120</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>113</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10">
@@ -1741,7 +1741,7 @@
         <v>30</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1801,7 +1801,7 @@
         <v>78</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>81</v>
@@ -1815,7 +1815,7 @@
         <v>123</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1918,7 +1918,7 @@
         <v>124</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1947,7 +1947,7 @@
         <v>30</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2007,7 +2007,7 @@
         <v>78</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>81</v>
@@ -2021,7 +2021,7 @@
         <v>125</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2044,16 +2044,16 @@
         <v>76</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2103,7 +2103,7 @@
         <v>76</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>83</v>
@@ -2118,7 +2118,7 @@
         <v>76</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>113</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -2215,21 +2215,21 @@
         <v>83</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>120</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>113</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2252,16 +2252,16 @@
         <v>76</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -2311,7 +2311,7 @@
         <v>76</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>83</v>
@@ -2326,7 +2326,7 @@
         <v>76</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>113</v>
+        <v>99</v>
       </c>
     </row>
     <row r="16">
@@ -2423,13 +2423,13 @@
         <v>83</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ16" t="s" s="2">
         <v>120</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>113</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>

--- a/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:10:14+00:00</t>
+    <t>2024-06-03T16:22:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:22:01+00:00</t>
+    <t>2024-06-03T16:23:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:23:50+00:00</t>
+    <t>2024-06-03T16:30:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:30:34+00:00</t>
+    <t>2024-06-05T12:07:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-05T12:07:44+00:00</t>
+    <t>2024-06-07T15:57:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-07T15:57:22+00:00</t>
+    <t>2024-07-01T19:46:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-01T19:46:33+00:00</t>
+    <t>2024-07-09T08:44:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T08:44:23+00:00</t>
+    <t>2024-07-10T09:54:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.1</t>
+    <t>1.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T09:54:14+00:00</t>
+    <t>2024-07-10T10:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T10:00:25+00:00</t>
+    <t>2024-07-10T10:02:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T10:02:38+00:00</t>
+    <t>2024-07-10T10:13:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T10:13:33+00:00</t>
+    <t>2024-07-10T12:01:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T12:01:49+00:00</t>
+    <t>2024-07-10T12:37:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T12:37:24+00:00</t>
+    <t>2024-07-10T13:09:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T13:09:17+00:00</t>
+    <t>2024-07-10T13:09:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T13:09:58+00:00</t>
+    <t>2024-07-10T13:27:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T13:27:13+00:00</t>
+    <t>2024-07-11T14:15:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-11T14:15:05+00:00</t>
+    <t>2024-07-11T14:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.0-snapshot</t>
+    <t>1.1.0-snapshot-2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-11T14:20:03+00:00</t>
+    <t>2024-07-11T15:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-11T15:32:47+00:00</t>
+    <t>2024-07-11T15:43:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-11T15:43:40+00:00</t>
+    <t>2024-07-11T16:04:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-11T16:04:15+00:00</t>
+    <t>2024-07-12T06:54:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-12T06:54:28+00:00</t>
+    <t>2024-07-12T07:24:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-27T17:01:01+00:00</t>
+    <t>2025-01-31T09:33:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-31T09:33:18+00:00</t>
+    <t>2025-02-03T16:26:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-03T16:26:04+00:00</t>
+    <t>2025-02-11T12:19:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T12:19:13+00:00</t>
+    <t>2025-02-11T12:46:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T12:46:26+00:00</t>
+    <t>2025-02-11T13:37:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T13:37:59+00:00</t>
+    <t>2025-02-11T14:09:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T14:09:44+00:00</t>
+    <t>2025-02-11T15:57:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T15:57:50+00:00</t>
+    <t>2025-02-11T16:04:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T16:04:30+00:00</t>
+    <t>2025-02-11T16:35:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-17T22:39:20+00:00</t>
+    <t>2025-02-24T08:37:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T08:37:03+00:00</t>
+    <t>2025-02-27T14:21:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-27T14:21:41+00:00</t>
+    <t>2025-02-27T14:23:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-27T14:23:05+00:00</t>
+    <t>2025-02-28T10:02:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-28T10:02:48+00:00</t>
+    <t>2025-03-05T17:59:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-05T17:59:44+00:00</t>
+    <t>2025-03-06T14:41:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T14:41:30+00:00</t>
+    <t>2025-03-06T14:56:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T14:56:25+00:00</t>
+    <t>2025-03-12T15:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-12T15:24:25+00:00</t>
+    <t>2025-03-18T14:02:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-18T14:02:39+00:00</t>
+    <t>2025-03-18T16:59:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-18T16:59:29+00:00</t>
+    <t>2025-03-21T10:50:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-snapshot-1</t>
+    <t>1.2.0-snapshot-2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T12:01:00+00:00</t>
+    <t>2026-06-19T13:53:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T13:53:04+00:00</t>
+    <t>2026-06-19T14:07:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T14:07:56+00:00</t>
+    <t>2026-06-23T09:20:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-23T09:20:47+00:00</t>
+    <t>2026-06-23T12:21:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-23T12:21:55+00:00</t>
+    <t>2026-06-26T10:36:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T10:36:05+00:00</t>
+    <t>2026-06-27T10:35:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-27T10:35:23+00:00</t>
+    <t>2026-06-30T07:59:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T07:59:11+00:00</t>
+    <t>2026-07-10T15:33:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-snapshot-2</t>
+    <t>1.2.0-snapshot-3</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T15:33:23+00:00</t>
+    <t>2026-07-10T15:46:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T15:46:03+00:00</t>
+    <t>2026-08-03T13:23:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T13:23:25+00:00</t>
+    <t>2026-08-03T14:28:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T14:28:09+00:00</t>
+    <t>2026-08-04T08:16:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
+++ b/main/ig/StructureDefinition-as-ext-organization-authorization-deadline.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T08:16:57+00:00</t>
+    <t>2026-08-04T12:10:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
